--- a/PDC.xlsx
+++ b/PDC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clases-r-daniel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Daniel\me recibo de sociologo 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374D7A40-1AE1-4CBD-BA2A-1F0A9EEAEE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9155C758-AB50-42AD-AC28-D565AB4A3633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="2655" windowWidth="22725" windowHeight="11295" xr2:uid="{EBAE3BF1-53C0-449F-A62A-44A1A7A3CC1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EBAE3BF1-53C0-449F-A62A-44A1A7A3CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablas" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="240">
   <si>
     <t>Edad</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Estadistico</t>
   </si>
   <si>
-    <t>Nivel educativo</t>
-  </si>
-  <si>
     <t>Modulo 1: descripcion de la muestra demografico</t>
   </si>
   <si>
@@ -66,15 +63,9 @@
     <t>Modulo 3: la tesis en sí</t>
   </si>
   <si>
-    <t>sexo</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
-    <t>edad</t>
-  </si>
-  <si>
     <t>Base: alumnos de sociolgia</t>
   </si>
   <si>
@@ -96,15 +87,6 @@
     <t>Alumnos según sexo y edad</t>
   </si>
   <si>
-    <t>Alumnos según nivel educativo y edad</t>
-  </si>
-  <si>
-    <t>Alumnos según nivel educativo</t>
-  </si>
-  <si>
-    <t>Edad promedio de los hijos de los alumnos de sociologia</t>
-  </si>
-  <si>
     <t>Promedio</t>
   </si>
   <si>
@@ -132,27 +114,6 @@
     <t>Alumnos según ocupacion con relacion a la carrera</t>
   </si>
   <si>
-    <t>Alumno horas de trabajo según genero</t>
-  </si>
-  <si>
-    <t>Alumno horas de trabajo según edad</t>
-  </si>
-  <si>
-    <t>Edad según condicion de actividad</t>
-  </si>
-  <si>
-    <t>Genero según condicion de actividad</t>
-  </si>
-  <si>
-    <t>Distribucion de generos por grupo de edad</t>
-  </si>
-  <si>
-    <t>Cantidad de horas trabajadas según grupos de edad</t>
-  </si>
-  <si>
-    <t>Cantidad de horas trabajadas según genero</t>
-  </si>
-  <si>
     <t>indice ritmo de cursada por genero</t>
   </si>
   <si>
@@ -165,78 +126,9 @@
     <t>Alumnos según situacion de convivencia</t>
   </si>
   <si>
-    <t>Alumnos según situacion habitacional</t>
-  </si>
-  <si>
     <t>Alumnos según situacion laboral actual</t>
   </si>
   <si>
-    <t>Alumnos según tipo de ocupacion</t>
-  </si>
-  <si>
-    <t>Alumno según tipo de registro de contratacion</t>
-  </si>
-  <si>
-    <t>Alumno según antigüedad laboral</t>
-  </si>
-  <si>
-    <t>Alumnos según carrera previa</t>
-  </si>
-  <si>
-    <t>alumnos según seminarios terminados</t>
-  </si>
-  <si>
-    <t>alumnos según acreditacion de horas de investigacion</t>
-  </si>
-  <si>
-    <t>alumnos según acreditacion de horas de practica profesional</t>
-  </si>
-  <si>
-    <t>alumnos según experiencia formacion por creditos</t>
-  </si>
-  <si>
-    <t>P. 36</t>
-  </si>
-  <si>
-    <t>alumnos según MOTIVOS DE NO CURSADO</t>
-  </si>
-  <si>
-    <t>P. 40, P. 41, P. 44</t>
-  </si>
-  <si>
-    <t>alumnos según RECURSADO DE TALLERES</t>
-  </si>
-  <si>
-    <t>P. 45, P. 46, P.47</t>
-  </si>
-  <si>
-    <t>alumnos según situacion actual</t>
-  </si>
-  <si>
-    <t>p. 48, P.49, P.50</t>
-  </si>
-  <si>
-    <t>ALUMNOS según grado dificultad de la tesina</t>
-  </si>
-  <si>
-    <t>P. 54, P. 55</t>
-  </si>
-  <si>
-    <t>P.23, P. 24, P. 25</t>
-  </si>
-  <si>
-    <t>P. 31</t>
-  </si>
-  <si>
-    <t>P. 32</t>
-  </si>
-  <si>
-    <t>P.33</t>
-  </si>
-  <si>
-    <t>P. 13</t>
-  </si>
-  <si>
     <t>Nombre cruce</t>
   </si>
   <si>
@@ -261,25 +153,610 @@
     <t>Alumnos según lugar de residencia y genero</t>
   </si>
   <si>
-    <t>p09</t>
-  </si>
-  <si>
     <t>Alumnos según situacion de convivencia y genero</t>
   </si>
   <si>
     <t>Alumnos según situacion de convivencia y edad</t>
   </si>
   <si>
-    <t>Alumnos según situacion habitacional  y genero</t>
-  </si>
-  <si>
-    <t>Alumnos según situacion habitacional  y edad</t>
-  </si>
-  <si>
     <t>p08_r</t>
   </si>
   <si>
     <t>nro_tabla</t>
+  </si>
+  <si>
+    <t>p11</t>
+  </si>
+  <si>
+    <t>p12</t>
+  </si>
+  <si>
+    <t>Alumnos según lugar de residencia y edad</t>
+  </si>
+  <si>
+    <t>p09_r</t>
+  </si>
+  <si>
+    <t>Alumnos según condicion de propiedad de la vivienda</t>
+  </si>
+  <si>
+    <t>Alumnos según condicion de propiedad de la vivienda y genero</t>
+  </si>
+  <si>
+    <t>Alumnos según condicion de propiedad de la vivienda y edad</t>
+  </si>
+  <si>
+    <t>Alumnos según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según sexo</t>
+  </si>
+  <si>
+    <t>Alumnos con hijos</t>
+  </si>
+  <si>
+    <t>p06</t>
+  </si>
+  <si>
+    <t>Alumnos edad hijo menor</t>
+  </si>
+  <si>
+    <t>Edad promedio de los hijos de los alumnos de sociologia según genero</t>
+  </si>
+  <si>
+    <t>Edad promedio de los hijos de los alumnos de sociologia según edad</t>
+  </si>
+  <si>
+    <t>p13</t>
+  </si>
+  <si>
+    <t>p14</t>
+  </si>
+  <si>
+    <t>Alumnos según ocupacion con relacion a la carrera según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según ocupacion con relacion a la carrera según genero</t>
+  </si>
+  <si>
+    <t>Alumnos según sector de trabajo</t>
+  </si>
+  <si>
+    <t>p15_r</t>
+  </si>
+  <si>
+    <t>Alumnos según sector de trabajo según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según sector de trabajo según genero</t>
+  </si>
+  <si>
+    <t>p16</t>
+  </si>
+  <si>
+    <t>Alumnos según para quien realiza trabajo principal</t>
+  </si>
+  <si>
+    <t>p17</t>
+  </si>
+  <si>
+    <t>Alumnos con ocupacion independiente</t>
+  </si>
+  <si>
+    <t>Alumnos con ocupacion independiente según edad</t>
+  </si>
+  <si>
+    <t>Alumnos con ocupacion independiente según genero</t>
+  </si>
+  <si>
+    <t>Alumnos según tipo de trabajo asalariado</t>
+  </si>
+  <si>
+    <t>p18</t>
+  </si>
+  <si>
+    <t>Alumnos según tipo de trabajo asalariado según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según tipo de trabajo asalariado según genero</t>
+  </si>
+  <si>
+    <t>Alumnos según condición de registro</t>
+  </si>
+  <si>
+    <t>p19_r</t>
+  </si>
+  <si>
+    <t>Alumnos según fecha de finalización</t>
+  </si>
+  <si>
+    <t>p20_r</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de horas semanales de trabajo</t>
+  </si>
+  <si>
+    <t>p21</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de horas semanales de trabajo según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de horas semanales de trabajo según genero</t>
+  </si>
+  <si>
+    <t>Alumnos según antigüedad laboral</t>
+  </si>
+  <si>
+    <t>p22</t>
+  </si>
+  <si>
+    <t>Alumnos según finalización de carrera terciaria o universitaria previa</t>
+  </si>
+  <si>
+    <t>p23</t>
+  </si>
+  <si>
+    <t>Alumnos según carrera terciaria o universitaria previa</t>
+  </si>
+  <si>
+    <t>p24</t>
+  </si>
+  <si>
+    <t>Alumnos según relacion del  trabajo actual con la carrera previa finalizada</t>
+  </si>
+  <si>
+    <t>p25</t>
+  </si>
+  <si>
+    <t>Alumnos según situacion laboral actual según edad</t>
+  </si>
+  <si>
+    <t>Alumnos según situacion laboral actual según genero</t>
+  </si>
+  <si>
+    <t>p27</t>
+  </si>
+  <si>
+    <t>Alumnos según año de ingreso a la carrera</t>
+  </si>
+  <si>
+    <t>Alumnos según cuatrimestre de ingreso a la carrera</t>
+  </si>
+  <si>
+    <t>p28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alumnos según condicion de graduacion </t>
+  </si>
+  <si>
+    <t>p29</t>
+  </si>
+  <si>
+    <t>Alumnos según realizacion de actividades del bloque de formacion por creditos</t>
+  </si>
+  <si>
+    <t>p30</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de seminarios de experiencia de oficios faltantes</t>
+  </si>
+  <si>
+    <t>p31</t>
+  </si>
+  <si>
+    <t>Alumnos según acreditacion de practicas profesionales</t>
+  </si>
+  <si>
+    <t>p32_r</t>
+  </si>
+  <si>
+    <t>Alumnos según acreditacion total de horas de investigación</t>
+  </si>
+  <si>
+    <t>p33_r</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de horas de investigación faltantes</t>
+  </si>
+  <si>
+    <t>p34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alumnos según nivel de acuerdo en la realizacion de las actividades del Bloque de Formacion por Credito </t>
+  </si>
+  <si>
+    <t>p35_1</t>
+  </si>
+  <si>
+    <t>p35_2</t>
+  </si>
+  <si>
+    <t>p35_3</t>
+  </si>
+  <si>
+    <t>p35_4</t>
+  </si>
+  <si>
+    <t>p35_5</t>
+  </si>
+  <si>
+    <t>p35_6</t>
+  </si>
+  <si>
+    <t>p35_7</t>
+  </si>
+  <si>
+    <t>p35_8</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos de no realizacion ninguna de las actividades del BFC</t>
+  </si>
+  <si>
+    <t>p36</t>
+  </si>
+  <si>
+    <t>p36_1</t>
+  </si>
+  <si>
+    <t>p36_2</t>
+  </si>
+  <si>
+    <t>p36_3</t>
+  </si>
+  <si>
+    <t>p36_4</t>
+  </si>
+  <si>
+    <t>p36_5</t>
+  </si>
+  <si>
+    <t>p37</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de materias faltantes del plan de estudio para finalizar la carrera</t>
+  </si>
+  <si>
+    <t>p37_r</t>
+  </si>
+  <si>
+    <t>Alumnos según etapa de la carrera actual</t>
+  </si>
+  <si>
+    <t>p38</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos principales de no comienzo del cursado del Taller 1</t>
+  </si>
+  <si>
+    <t>p39</t>
+  </si>
+  <si>
+    <t>p39_1</t>
+  </si>
+  <si>
+    <t>p39_2</t>
+  </si>
+  <si>
+    <t>p39_3</t>
+  </si>
+  <si>
+    <t>p39_4</t>
+  </si>
+  <si>
+    <t>p39_5</t>
+  </si>
+  <si>
+    <t>p39_6</t>
+  </si>
+  <si>
+    <t>p39_7</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos principales de no comienzo del cursado del Taller 2</t>
+  </si>
+  <si>
+    <t>p40</t>
+  </si>
+  <si>
+    <t>p40_1</t>
+  </si>
+  <si>
+    <t>p40_2</t>
+  </si>
+  <si>
+    <t>p40_3</t>
+  </si>
+  <si>
+    <t>p40_4</t>
+  </si>
+  <si>
+    <t>p40_5</t>
+  </si>
+  <si>
+    <t>p40_6</t>
+  </si>
+  <si>
+    <t>p40_7</t>
+  </si>
+  <si>
+    <t>p40_8</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos principales de no comienzo del cursado del Taller 3</t>
+  </si>
+  <si>
+    <t>p41</t>
+  </si>
+  <si>
+    <t>p41_1</t>
+  </si>
+  <si>
+    <t>p41_2</t>
+  </si>
+  <si>
+    <t>p41_3</t>
+  </si>
+  <si>
+    <t>p41_4</t>
+  </si>
+  <si>
+    <t>p41_5</t>
+  </si>
+  <si>
+    <t>p41_6</t>
+  </si>
+  <si>
+    <t>p41_7</t>
+  </si>
+  <si>
+    <t>p41_8</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de materias obligatorias u optativas cursadas actualmente</t>
+  </si>
+  <si>
+    <t>p42</t>
+  </si>
+  <si>
+    <t>Alumnos según fecha de ultima vez que cursaron materias obligatorias u optativas</t>
+  </si>
+  <si>
+    <t>p43</t>
+  </si>
+  <si>
+    <t>Alumnos según los motivos de no cursado actual de materias obligatorias u optativas</t>
+  </si>
+  <si>
+    <t>p44</t>
+  </si>
+  <si>
+    <t>p44_1</t>
+  </si>
+  <si>
+    <t>p44_2</t>
+  </si>
+  <si>
+    <t>p44_3</t>
+  </si>
+  <si>
+    <t>p44_1r</t>
+  </si>
+  <si>
+    <t>p44_2r</t>
+  </si>
+  <si>
+    <t>p44_3r</t>
+  </si>
+  <si>
+    <t>Alumnos según cursado mas de una vez algun taller</t>
+  </si>
+  <si>
+    <t>p45</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de veces curso cada uno de los talleres</t>
+  </si>
+  <si>
+    <t>p46_1</t>
+  </si>
+  <si>
+    <t>p46_2</t>
+  </si>
+  <si>
+    <t>p46_3</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos principales del cursado de los talleres mas de una vez</t>
+  </si>
+  <si>
+    <t>p47</t>
+  </si>
+  <si>
+    <t>p47_1r</t>
+  </si>
+  <si>
+    <t>p47_2r</t>
+  </si>
+  <si>
+    <t>p47_3r</t>
+  </si>
+  <si>
+    <t>p47_4r</t>
+  </si>
+  <si>
+    <t>Alumnos según condicion actual en la carrera</t>
+  </si>
+  <si>
+    <t>p48</t>
+  </si>
+  <si>
+    <t>Alumnos según iniciacion de actividades vinculadas a la tesina</t>
+  </si>
+  <si>
+    <t>p49</t>
+  </si>
+  <si>
+    <t>Alumnos según actividades de la tesina completadas</t>
+  </si>
+  <si>
+    <t>p50</t>
+  </si>
+  <si>
+    <t>p50_1</t>
+  </si>
+  <si>
+    <t>p50_2</t>
+  </si>
+  <si>
+    <t>p50_3</t>
+  </si>
+  <si>
+    <t>p50_4</t>
+  </si>
+  <si>
+    <t>p50_5</t>
+  </si>
+  <si>
+    <t>p50_6</t>
+  </si>
+  <si>
+    <t>p50_7</t>
+  </si>
+  <si>
+    <t>p50_8</t>
+  </si>
+  <si>
+    <t>Alumnos según fecha aproximada de finalizacion de la tesina</t>
+  </si>
+  <si>
+    <t>p51</t>
+  </si>
+  <si>
+    <t>Alumnos según cantidad de meses entre finalizacion del taller 3 y entrega de la tesina</t>
+  </si>
+  <si>
+    <t>p52</t>
+  </si>
+  <si>
+    <t>Alumnos según grado de dificultad para el avance de la tesina</t>
+  </si>
+  <si>
+    <t>p53_1</t>
+  </si>
+  <si>
+    <t>p53_2</t>
+  </si>
+  <si>
+    <t>p53_3</t>
+  </si>
+  <si>
+    <t>p53_4</t>
+  </si>
+  <si>
+    <t>p53_5</t>
+  </si>
+  <si>
+    <t>p53_6</t>
+  </si>
+  <si>
+    <t>p53_7</t>
+  </si>
+  <si>
+    <t>p53_8</t>
+  </si>
+  <si>
+    <t>p54_1</t>
+  </si>
+  <si>
+    <t>p54_2</t>
+  </si>
+  <si>
+    <t>p54_3</t>
+  </si>
+  <si>
+    <t>p54_4</t>
+  </si>
+  <si>
+    <t>Alumnos según frecuencia de experimentacion</t>
+  </si>
+  <si>
+    <t>p55_1</t>
+  </si>
+  <si>
+    <t>p55_2</t>
+  </si>
+  <si>
+    <t>p55_3</t>
+  </si>
+  <si>
+    <t>p55_4</t>
+  </si>
+  <si>
+    <t>p55_5</t>
+  </si>
+  <si>
+    <t>p55_6</t>
+  </si>
+  <si>
+    <t>p55_7</t>
+  </si>
+  <si>
+    <t>p55_8</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos de eleccion de la carrera</t>
+  </si>
+  <si>
+    <t>p56_1</t>
+  </si>
+  <si>
+    <t>p56_2</t>
+  </si>
+  <si>
+    <t>p56_3</t>
+  </si>
+  <si>
+    <t>p56_4</t>
+  </si>
+  <si>
+    <t>p56_5</t>
+  </si>
+  <si>
+    <t>p56_6</t>
+  </si>
+  <si>
+    <t>p56_7</t>
+  </si>
+  <si>
+    <t>p56_8</t>
+  </si>
+  <si>
+    <t>Alumnos según motivos de finalizacion de la carrera</t>
+  </si>
+  <si>
+    <t>p57_1</t>
+  </si>
+  <si>
+    <t>p57_2</t>
+  </si>
+  <si>
+    <t>p57_3</t>
+  </si>
+  <si>
+    <t>p57_4</t>
+  </si>
+  <si>
+    <t>p57_5</t>
+  </si>
+  <si>
+    <t>p57_6</t>
+  </si>
+  <si>
+    <t>p13_r</t>
+  </si>
+  <si>
+    <t>p27_r</t>
   </si>
 </sst>
 </file>
@@ -309,7 +786,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +802,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,15 +839,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -700,26 +1188,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EF7864-3023-4A15-8F25-421ACB460560}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.140625" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -728,397 +1217,1203 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
         <v>77</v>
       </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>78</v>
       </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="4" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="7"/>
+      <c r="C65" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" t="s">
-        <v>60</v>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>125</v>
+      </c>
+      <c r="C82" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>129</v>
+      </c>
+      <c r="C84" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>148</v>
+      </c>
+      <c r="C101" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>158</v>
+      </c>
+      <c r="C110" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>160</v>
+      </c>
+      <c r="C111" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>162</v>
+      </c>
+      <c r="C112" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C113" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C114" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C115" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>170</v>
+      </c>
+      <c r="C119" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>172</v>
+      </c>
+      <c r="C120" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C121" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C122" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>176</v>
+      </c>
+      <c r="C123" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C124" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C125" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C126" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>182</v>
+      </c>
+      <c r="C128" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>184</v>
+      </c>
+      <c r="C129" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>186</v>
+      </c>
+      <c r="C130" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C131" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C132" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C133" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C134" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C135" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C136" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C137" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C138" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>196</v>
+      </c>
+      <c r="C139" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>198</v>
+      </c>
+      <c r="C140" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>200</v>
+      </c>
+      <c r="C141" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C142" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C143" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C144" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C145" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C146" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C147" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C148" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>200</v>
+      </c>
+      <c r="C149" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C150" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C151" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C152" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>213</v>
+      </c>
+      <c r="C153" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C154" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C155" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C156" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C157" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C158" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C159" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C160" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>222</v>
+      </c>
+      <c r="C161" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C162" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C163" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C164" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C165" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C166" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C167" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C168" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>231</v>
+      </c>
+      <c r="C169" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C170" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C171" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C172" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C173" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C174" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="B36:G36"/>
+  <mergeCells count="2">
+    <mergeCell ref="B50:G50"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1133,7 +2428,7 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -1141,15 +2436,15 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1161,7 +2456,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -1169,15 +2464,15 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2"/>
     </row>
